--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>871116</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>834540</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>802273</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>731290</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>725816</v>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>712500</v>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -473,9 +450,6 @@
       </c>
       <c r="B8">
         <v>644800</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>871116</v>
       </c>
+      <c r="C2">
+        <v>753540</v>
+      </c>
+      <c r="D2">
+        <v>117576</v>
+      </c>
+      <c r="E2">
+        <v>15.60315311728642</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,54 +410,109 @@
       <c r="B3">
         <v>834540</v>
       </c>
+      <c r="C3">
+        <v>695866</v>
+      </c>
+      <c r="D3">
+        <v>138674</v>
+      </c>
+      <c r="E3">
+        <v>19.92826205045224</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B4">
-        <v>802273</v>
+        <v>811680</v>
+      </c>
+      <c r="C4">
+        <v>708603</v>
+      </c>
+      <c r="D4">
+        <v>103077</v>
+      </c>
+      <c r="E4">
+        <v>14.5465091172349</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="B5">
-        <v>731290</v>
+        <v>802273</v>
+      </c>
+      <c r="C5">
+        <v>679122.5</v>
+      </c>
+      <c r="D5">
+        <v>123150.5</v>
+      </c>
+      <c r="E5">
+        <v>18.13376820823931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colchane</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="B6">
-        <v>725816</v>
+        <v>731290</v>
+      </c>
+      <c r="C6">
+        <v>646250</v>
+      </c>
+      <c r="D6">
+        <v>85040</v>
+      </c>
+      <c r="E6">
+        <v>13.15899419729207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Colchane</t>
         </is>
       </c>
       <c r="B7">
-        <v>712500</v>
+        <v>725816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>712500</v>
+      </c>
+      <c r="C8">
+        <v>634709</v>
+      </c>
+      <c r="D8">
+        <v>77791</v>
+      </c>
+      <c r="E8">
+        <v>12.25616778712764</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Camiña</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>644800</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_tarapaca.xlsx
@@ -523,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -532,40 +532,26 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>731290</v>
+          <t>Camiña</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Camiña</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>644800</v>
+          <t>Colchane</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colchane</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>725816</v>
+          <t>Pozo Almonte</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -574,38 +560,26 @@
           <t>Huara</t>
         </is>
       </c>
-      <c r="B5">
-        <v>712500</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>871116</v>
+          <t>Alto Hospicio</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>802273</v>
+          <t>Iquique</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>834540</v>
+          <t>Pica</t>
+        </is>
       </c>
     </row>
   </sheetData>
